--- a/Result/profitability/2482.xlsx
+++ b/Result/profitability/2482.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1925</v>
+        <v>-0.21375</v>
       </c>
       <c r="N2" t="n">
-        <v>38.5</v>
+        <v>38.80374999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.12875</v>
+        <v>-0.17625</v>
       </c>
       <c r="N3" t="n">
-        <v>37.4975</v>
+        <v>39.5025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.13375</v>
+        <v>-0.135</v>
       </c>
       <c r="N4" t="n">
-        <v>38.87625000000001</v>
+        <v>39.39375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.13375</v>
+        <v>-0.08124999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>37.89375</v>
+        <v>38.13125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04125</v>
+        <v>-0.075</v>
       </c>
       <c r="N6" t="n">
-        <v>36.70875</v>
+        <v>35.64</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.003749999999999996</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="N7" t="n">
-        <v>34.46875</v>
+        <v>35.38</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>0.06125000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>34.75375</v>
+        <v>35.36125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.09875</v>
       </c>
       <c r="N9" t="n">
-        <v>34.11499999999999</v>
+        <v>34.115</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2482</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>120</v>
+      </c>
+      <c r="D75" t="n">
+        <v>68</v>
+      </c>
+      <c r="E75" t="n">
+        <v>52</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-22.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.58625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.859999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.127092050209205</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6461538461538461</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0461165048543688</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
